--- a/SEAN_TRACKER_MASTER.xlsx
+++ b/SEAN_TRACKER_MASTER.xlsx
@@ -1957,42 +1957,46 @@
       <c r="L36" s="16" t="n"/>
     </row>
     <row r="37" ht="45" customHeight="1" s="11">
-      <c r="A37" s="13" t="n">
+      <c r="A37" s="25" t="n">
         <v>46304</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Full E2E test: RFID scan -&gt; Android dedup -&gt; Odoo bridge -&gt; scan UI -&gt; stock.quant adjustment, verified against the audit trail.</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Full E2E test: RFID scan -&gt; Android dedup -&gt; direct XML-RPC/JSON-RPC to Odoo -&gt; stock.lot.name match -&gt; stock.quant adjustment, verified against stock.move history. (Originally routed through a custom Odoo bridge + scan UI -- superseded, see roadmap Section 9.)</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>End-to-end flow verified; every scan traceable in stock.barcode.rfid.scan.</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L37" s="14" t="n"/>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Path corrected from 'Odoo bridge -&gt; scan UI' (superseded architecture) to direct XML-RPC.</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="n"/>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="n"/>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n"/>
     </row>
     <row r="38" ht="45" customHeight="1" s="11">
       <c r="A38" s="15" t="n">
@@ -2033,42 +2037,46 @@
       <c r="L38" s="16" t="n"/>
     </row>
     <row r="39" ht="45" customHeight="1" s="11">
-      <c r="A39" s="13" t="n">
+      <c r="A39" s="25" t="n">
         <v>46308</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Load + security + performance pass: 200+ tag dense-shelf sweep, auth bypass attempt on /scan, latency check (&lt;100ms p95, ≥50 EPCs/sec).</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Load + security + performance pass: 200+ tag dense-shelf sweep, verify the Odoo user account used for XML-RPC has least-privilege access (not an admin account), latency check on the XML-RPC round trip (&lt;100ms p95, &gt;=50 EPCs/sec). (Originally an auth-bypass test against a custom /scan endpoint -- not applicable, no such endpoint exists under the current architecture.)</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Load/security/performance report against all three targets.</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="n"/>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L39" s="14" t="n"/>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Security test target corrected -- no /scan endpoint exists to bypass under direct XML-RPC; real risk is XML-RPC credential scope instead.</t>
+        </is>
+      </c>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="n"/>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n"/>
     </row>
     <row r="40" ht="45" customHeight="1" s="11">
       <c r="A40" s="15" t="n">
@@ -2273,7 +2281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -2305,84 +2313,96 @@
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" s="11">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>Holiday handling</t>
-        </is>
-      </c>
-      <c r="B3" s="22" t="inlineStr">
-        <is>
-          <t>Philippine 2026 public holidays per Proclamation No. 1006 are shown as explicit HOLIDAY rows (not silently skipped), so the schedule is auditable. National Heroes Day (Aug 31, 2026) is the only regular holiday inside the project window.</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Architecture pivot (2026-08-26)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Per direction, the custom stock_barcode_rfid controller architecture in Section 2 was overridden by Desktop 1's Option 3 (direct XML-RPC from the Android app). Tracker rows describing the old design are marked Superseded or Done (module inactive) rather than deleted. Full rationale in rfid-odoo-roadmap-MASTER.docx Section 9.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" s="11">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>EPC mapping model</t>
+          <t>Holiday handling</t>
         </is>
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>rfid.tag.mapping + standard Barcode/Serial Number fields on product.product. Barcode Nomenclature and EPC-&gt;stock.lot.name are NOT used — they cannot represent an unresolved/unknown EPC.</t>
+          <t>Philippine 2026 public holidays per Proclamation No. 1006 are shown as explicit HOLIDAY rows (not silently skipped), so the schedule is auditable. National Heroes Day (Aug 31, 2026) is the only regular holiday inside the project window.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="11">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>EPC mapping model</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>iData T1UHF exclusively. Any Zebra or DataWedge reference appearing in future edits of this tracker is contamination and should be removed on sight.</t>
+          <t>ORIGINAL DESIGN (superseded, code retained inactive): rfid.tag.mapping + standard Barcode/Serial Number fields on product.product. CURRENT (as of 2026-08-26 addendum): direct match against stock.lot.name via XML-RPC/JSON-RPC from the Android app (no custom Odoo controller). This reintroduces the unresolved/unknown-EPC gap the original design existed to avoid; that gap is now handled on-device via UnresolvedScanStore (android/app/.../scanner/UnresolvedScanStore.kt), not server-side. See rfid-odoo-roadmap-MASTER.docx Section 9.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" s="11">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>Auth pattern</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Odoo API key checked inside the controller (auth='public' + manual header check against res.users.apikeys). auth='bearer' is not a real Odoo route auth type.</t>
+          <t>iData T1UHF exclusively. Any Zebra or DataWedge reference appearing in future edits of this tracker is contamination and should be removed on sight.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" s="11">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>Scope boundary</t>
+          <t>Auth pattern</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Ends at Pilot/UAT go/no-go. Production Rollout is explicitly out of scope for this OJT engagement and is not scheduled here.</t>
+          <t>ORIGINAL DESIGN (superseded, code retained inactive): Odoo API key checked inside the controller (auth='public' + manual header check against res.users.apikeys). auth='bearer' is not a real Odoo route auth type. CURRENT: not applicable -- the Android app authenticates to Odoo's XML-RPC/JSON-RPC API directly as an Odoo user, no custom API key scheme.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" s="11">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>Status values</t>
+          <t>Scope boundary</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Completed / In Progress / Not Started / Blocked / N/A (holiday rows).</t>
+          <t>Ends at Pilot/UAT go/no-go. Production Rollout is explicitly out of scope for this OJT engagement and is not scheduled here.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="11">
       <c r="A9" s="21" t="inlineStr">
         <is>
+          <t>Status values</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Completed / In Progress / Not Started / Blocked / N/A (holiday rows).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
           <t>% Progress</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>0 / 25 / 50 / 75 / 100.</t>
         </is>

--- a/SEAN_TRACKER_MASTER.xlsx
+++ b/SEAN_TRACKER_MASTER.xlsx
@@ -72,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +115,12 @@
         <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +156,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -228,6 +234,12 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,42 +575,46 @@
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" s="11">
-      <c r="A2" s="13" t="n">
+      <c r="A2" s="27" t="n">
         <v>46258</v>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Confirm Phase 0 decisions log against locked constraints (T1UHF-only, Community, rfid.tag.mapping, Pilot/UAT scope).</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>Confirmed via chat: T1UHF-only, Community edition, Pilot/UAT scope, and (until the 2026-08-26 pivot) the rfid.tag.mapping design all cross-checked against rfid-odoo-roadmap-MASTER.docx Section 2 before any code was written.</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>Signed-off Phase 0 decisions matching rfid-odoo-roadmap-MASTER.docx Section 2.</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L2" s="14" t="n"/>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="28" t="n"/>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="28" t="inlineStr">
+        <is>
+          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
+        </is>
+      </c>
+      <c r="J2" s="28" t="n"/>
+      <c r="K2" s="28" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="n"/>
     </row>
     <row r="3" ht="45" customHeight="1" s="11">
       <c r="A3" s="15" t="n">
@@ -639,42 +655,46 @@
       <c r="L3" s="16" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1" s="11">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="19" t="n">
         <v>46260</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Scaffold stock_barcode_rfid Odoo module (manifest, models/, controllers/, views/, security/, tests/).</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Manifest, models/ (rfid.tag.mapping, stock.barcode.rfid.scan), controllers/ (POST /stock_barcode_rfid/scan), security/ir.model.access.csv all built and pushed. Module later marked inactive by the 2026-08-26 pivot -- code retained, not deleted.</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Empty module installs without errors.</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="n"/>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Done (module inactive -- see 2026-08-26 addendum)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1" s="11">
       <c r="A5" s="15" t="n">
@@ -783,42 +803,46 @@
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="11">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="19" t="n">
         <v>46266</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Source and import the iData T1UHF SDK (.aar/.jar); resolve Gradle dependencies; smoke-test SDK init on the physical device.</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>UHFJar_V1.4.05.aar + native libs (libjni_rfid_driver.so, libserialportJni.so for arm64-v8a/armeabi-v7a) identified as the correct iData-branded SDK (of 3 IT-provided candidates) and committed into android/app/libs and jniLibs. Demo APK (UHFDemo_v1.2.534) provided for on-device sideload. Smoke test on the physical T1UHF unit not yet confirmed back.</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>SDK initializes; device responds to open()/powerOn()-equivalent call. CRITICAL PATH ITEM.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L8" s="14" t="n"/>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Sideload UHFDemo_v1.2.534 APK onto the physical T1UHF and confirm scan/inventory works.</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1" s="11">
       <c r="A9" s="19" t="n">
@@ -1341,7 +1365,11 @@
           <t>Discrepancies view: list all stock.barcode.rfid.scan rows with status='unknown' for operator resolution (Ventor 'Discrepancies' pattern).</t>
         </is>
       </c>
-      <c r="C21" s="24" t="n"/>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Replacement built: UnresolvedScanStore.kt (local SQLite) logs every EPC that fails to match, so operators can still review unresolved tags. This is the on-device equivalent of the original server-side Discrepancies view.</t>
+        </is>
+      </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
           <t>View shows unresolved EPCs with product context where available.</t>
@@ -1349,11 +1377,11 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Superseded (see 2026-08-26 addendum)</t>
+          <t>Superseded -- replacement implemented (see 2026-08-26 addendum)</t>
         </is>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>

--- a/SEAN_TRACKER_MASTER.xlsx
+++ b/SEAN_TRACKER_MASTER.xlsx
@@ -735,42 +735,50 @@
       <c r="L5" s="16" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1" s="11">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="19" t="n">
         <v>46262</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Scaffold Android project (Kotlin); package structure; Git branch strategy.</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Per Desktop 1: an Android app (RfidScannerApp2, Java, package com.manilainvestments.rfidscanner, using UHFManager/UM_MODULE) has started -- exact current state not yet confirmed against this repo.</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Android project builds; repo structure matches monorepo convention.</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>See rfid-odoo-roadmap-MASTER.docx for phase context.</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L6" s="14" t="n"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Real app lives in a separate session (Desktop 1), not yet merged into this repo. This repo's android/ folder is still the older, unrelated Kotlin skeleton (com.idataproject).</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Confirm RfidScannerApp2’s current state with Vin and merge the real project files into this repo’s android/ folder.</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1" s="11">
       <c r="A7" s="17" t="n">

--- a/SEAN_TRACKER_MASTER.xlsx
+++ b/SEAN_TRACKER_MASTER.xlsx
@@ -611,7 +611,7 @@
       <c r="J2" s="28" t="n"/>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Adequate. Constraints were cross-checked against the roadmap before any code was written, which is the right order of operations -- low risk of rework from this step.</t>
         </is>
       </c>
       <c r="L2" s="28" t="n"/>
@@ -691,7 +691,7 @@
       <c r="J4" s="20" t="n"/>
       <c r="K4" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Technically clean at the time it was built (correct manifest, no Enterprise deps). Value is now moot since the module was superseded hours later -- not wasted effort, but a sign of how fast the direction changed this week.</t>
         </is>
       </c>
       <c r="L4" s="20" t="n"/>
@@ -775,7 +775,7 @@
       <c r="J6" s="20" t="n"/>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Real gap: this work is happening in an un-synced separate session (Desktop 1). Until those files are merged here, this repo does not actually have a working Android scaffold. This is a coordination risk, not a technical one -- flag it as such.</t>
         </is>
       </c>
       <c r="L6" s="20" t="n"/>
@@ -847,7 +847,7 @@
       <c r="J8" s="20" t="n"/>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>SDK selection was done properly -- cross-referenced 3 candidates against actual doc content instead of trusting filenames. But the step that actually matters (does it work on the real device) is still unconfirmed. Do not close this out until that smoke test comes back positive.</t>
         </is>
       </c>
       <c r="L8" s="20" t="n"/>
@@ -899,7 +899,11 @@
           <t>See rfid-odoo-roadmap-MASTER.docx Section 9 for full rationale.</t>
         </is>
       </c>
-      <c r="K9" s="20" t="n"/>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>Necessary and well-executed. Documenting an architecture reversal instead of silently overwriting the roadmap avoids confusion for whoever picks this up next.</t>
+        </is>
+      </c>
       <c r="L9" s="20" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1" s="11">
@@ -939,7 +943,7 @@
       <c r="J10" s="20" t="n"/>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design was correct for its time (lot_id optional, EPC unique). Now inactive, but worth keeping -- if Option 3 runs into the unresolved-EPC problem during the pilot, this is a ready fallback.</t>
         </is>
       </c>
       <c r="L10" s="20" t="n"/>
@@ -981,7 +985,7 @@
       <c r="J11" s="20" t="n"/>
       <c r="K11" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>The stock.inventory -&gt; stock.location catch (Odoo 14+ removed that model) shows this was actually checked against the real Odoo 19 API, not written from memory. Good catch, now sitting unused.</t>
         </is>
       </c>
       <c r="L11" s="20" t="n"/>
@@ -1065,7 +1069,7 @@
       <c r="J13" s="20" t="n"/>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Tests are written, not run -- there is no Docker/Odoo environment in this project yet. Treat 'Done' here as 'written', not 'passing'.</t>
         </is>
       </c>
       <c r="L13" s="20" t="n"/>
@@ -1107,7 +1111,7 @@
       <c r="J14" s="20" t="n"/>
       <c r="K14" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Endpoint is correctly built but is dead code under Option 3. No harm keeping it, but don't let it drift out of sync if anyone touches it later.</t>
         </is>
       </c>
       <c r="L14" s="20" t="n"/>
@@ -1149,7 +1153,7 @@
       <c r="J15" s="24" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L15" s="24" t="n"/>
@@ -1191,7 +1195,7 @@
       <c r="J16" s="24" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L16" s="24" t="n"/>
@@ -1233,7 +1237,7 @@
       <c r="J17" s="24" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L17" s="24" t="n"/>
@@ -1275,7 +1279,7 @@
       <c r="J18" s="24" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L18" s="24" t="n"/>
@@ -1317,7 +1321,7 @@
       <c r="J19" s="24" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L19" s="24" t="n"/>
@@ -1359,7 +1363,7 @@
       <c r="J20" s="24" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L20" s="24" t="n"/>
@@ -1405,7 +1409,7 @@
       <c r="J21" s="24" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>The most important remark on this sheet: Option 3 does not by itself guarantee the "never silently drop an EPC" success criterion. UnresolvedScanStore is built, but not yet called from any actual scan loop -- it is a solution sitting on a shelf until the real Android code wires it in.</t>
         </is>
       </c>
       <c r="L21" s="24" t="n"/>
@@ -1447,7 +1451,7 @@
       <c r="J22" s="24" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L22" s="24" t="n"/>
@@ -1489,7 +1493,7 @@
       <c r="J23" s="24" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Correctly superseded, no code debt.</t>
         </is>
       </c>
       <c r="L23" s="24" t="n"/>
@@ -2317,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -2444,6 +2448,18 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supervisor / Remarks column (as of 2026-08-26)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Entries filled in for rows with actual progress are Claude's own technical review of the work (code quality, real risks, what's still unverified) -- not an official human supervisor's sign-off. Your actual OJT supervisor should still review and countersign separately; do not submit this column as-is as their approval.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
